--- a/assets/evaluationkit-rawdata.xlsx
+++ b/assets/evaluationkit-rawdata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davisjam/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davisjam/Downloads/purdue-tenure-packet-generator/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C070E42-0BC4-2247-B0F2-E25876768FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515CA7F9-2A22-A94D-9428-CC25A66B044D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5743" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6198" uniqueCount="147">
   <si>
     <t>Project</t>
   </si>
@@ -393,17 +393,92 @@
   <si>
     <t>737250-0</t>
   </si>
+  <si>
+    <t>Fall 2021 Core -4 16 Week 11/29-12/12</t>
+  </si>
+  <si>
+    <t>wl.202210.VIP.47920.023.10351</t>
+  </si>
+  <si>
+    <t>614817-0</t>
+  </si>
+  <si>
+    <t>Fall 2021 Core -4 16 Week 11/29-12/12 Co-admin</t>
+  </si>
+  <si>
+    <t>wl.202210.ECE.46100.001.25466</t>
+  </si>
+  <si>
+    <t>614818-0</t>
+  </si>
+  <si>
+    <t>614819-0</t>
+  </si>
+  <si>
+    <t>614821-0</t>
+  </si>
+  <si>
+    <t>614822-0</t>
+  </si>
+  <si>
+    <t>614823-0</t>
+  </si>
+  <si>
+    <t>614824-0</t>
+  </si>
+  <si>
+    <t>614825-0</t>
+  </si>
+  <si>
+    <t>614826-0</t>
+  </si>
+  <si>
+    <t>Fall 2022 Core -4 16 Week 11/28-12/11</t>
+  </si>
+  <si>
+    <t>wl.202310.VIP.47920.023.10351</t>
+  </si>
+  <si>
+    <t>679118-0</t>
+  </si>
+  <si>
+    <t>679119-0</t>
+  </si>
+  <si>
+    <t>679120-0</t>
+  </si>
+  <si>
+    <t>679121-0</t>
+  </si>
+  <si>
+    <t>679122-0</t>
+  </si>
+  <si>
+    <t>679123-0</t>
+  </si>
+  <si>
+    <t>679124-0</t>
+  </si>
+  <si>
+    <t>679125-0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -427,8 +502,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q819"/>
+  <dimension ref="A1:Q898"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -44173,6 +44249,3997 @@
         <v>0.88456652947900005</v>
       </c>
     </row>
+    <row r="820" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A820" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C820" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E820" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F820" s="1">
+        <v>10</v>
+      </c>
+      <c r="G820" s="1">
+        <v>9</v>
+      </c>
+      <c r="H820" s="1">
+        <v>90</v>
+      </c>
+      <c r="I820" s="1">
+        <v>4.3333334900000002</v>
+      </c>
+      <c r="J820" s="1">
+        <v>0.70710677</v>
+      </c>
+      <c r="K820" s="1">
+        <v>5</v>
+      </c>
+      <c r="L820" s="1">
+        <v>4</v>
+      </c>
+      <c r="M820" s="1">
+        <v>44.444442700000003</v>
+      </c>
+      <c r="N820" s="1"/>
+      <c r="O820" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P820" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q820" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="821" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A821" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C821" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E821" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F821" s="1">
+        <v>10</v>
+      </c>
+      <c r="G821" s="1">
+        <v>9</v>
+      </c>
+      <c r="H821" s="1">
+        <v>90</v>
+      </c>
+      <c r="I821" s="1">
+        <v>4.3333334900000002</v>
+      </c>
+      <c r="J821" s="1">
+        <v>0.70710677</v>
+      </c>
+      <c r="K821" s="1">
+        <v>4</v>
+      </c>
+      <c r="L821" s="1">
+        <v>4</v>
+      </c>
+      <c r="M821" s="1">
+        <v>44.444442700000003</v>
+      </c>
+      <c r="N821" s="1"/>
+      <c r="O821" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P821" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q821" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="822" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A822" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E822" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F822" s="1">
+        <v>10</v>
+      </c>
+      <c r="G822" s="1">
+        <v>9</v>
+      </c>
+      <c r="H822" s="1">
+        <v>90</v>
+      </c>
+      <c r="I822" s="1">
+        <v>4.3333334900000002</v>
+      </c>
+      <c r="J822" s="1">
+        <v>0.70710677</v>
+      </c>
+      <c r="K822" s="1">
+        <v>3</v>
+      </c>
+      <c r="L822" s="1">
+        <v>1</v>
+      </c>
+      <c r="M822" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N822" s="1"/>
+      <c r="O822" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P822" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q822" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="823" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A823" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E823" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F823" s="1">
+        <v>72</v>
+      </c>
+      <c r="G823" s="1">
+        <v>36</v>
+      </c>
+      <c r="H823" s="1">
+        <v>50</v>
+      </c>
+      <c r="I823" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J823" s="1">
+        <v>1.1450376499999999</v>
+      </c>
+      <c r="K823" s="1">
+        <v>5</v>
+      </c>
+      <c r="L823" s="1">
+        <v>13</v>
+      </c>
+      <c r="M823" s="1">
+        <v>36.111110699999998</v>
+      </c>
+      <c r="N823" s="1"/>
+      <c r="O823" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P823" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q823" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="824" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A824" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E824" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F824" s="1">
+        <v>72</v>
+      </c>
+      <c r="G824" s="1">
+        <v>36</v>
+      </c>
+      <c r="H824" s="1">
+        <v>50</v>
+      </c>
+      <c r="I824" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J824" s="1">
+        <v>1.1450376499999999</v>
+      </c>
+      <c r="K824" s="1">
+        <v>4</v>
+      </c>
+      <c r="L824" s="1">
+        <v>15</v>
+      </c>
+      <c r="M824" s="1">
+        <v>41.6666679</v>
+      </c>
+      <c r="N824" s="1"/>
+      <c r="O824" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P824" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q824" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="825" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A825" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C825" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E825" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F825" s="1">
+        <v>72</v>
+      </c>
+      <c r="G825" s="1">
+        <v>36</v>
+      </c>
+      <c r="H825" s="1">
+        <v>50</v>
+      </c>
+      <c r="I825" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J825" s="1">
+        <v>1.1450376499999999</v>
+      </c>
+      <c r="K825" s="1">
+        <v>3</v>
+      </c>
+      <c r="L825" s="1">
+        <v>3</v>
+      </c>
+      <c r="M825" s="1">
+        <v>8.3333330199999995</v>
+      </c>
+      <c r="N825" s="1"/>
+      <c r="O825" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P825" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q825" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="826" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A826" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E826" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F826" s="1">
+        <v>72</v>
+      </c>
+      <c r="G826" s="1">
+        <v>36</v>
+      </c>
+      <c r="H826" s="1">
+        <v>50</v>
+      </c>
+      <c r="I826" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J826" s="1">
+        <v>1.1450376499999999</v>
+      </c>
+      <c r="K826" s="1">
+        <v>2</v>
+      </c>
+      <c r="L826" s="1">
+        <v>3</v>
+      </c>
+      <c r="M826" s="1">
+        <v>8.3333330199999995</v>
+      </c>
+      <c r="N826" s="1"/>
+      <c r="O826" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P826" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q826" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="827" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A827" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E827" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F827" s="1">
+        <v>72</v>
+      </c>
+      <c r="G827" s="1">
+        <v>36</v>
+      </c>
+      <c r="H827" s="1">
+        <v>50</v>
+      </c>
+      <c r="I827" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J827" s="1">
+        <v>1.1450376499999999</v>
+      </c>
+      <c r="K827" s="1">
+        <v>1</v>
+      </c>
+      <c r="L827" s="1">
+        <v>2</v>
+      </c>
+      <c r="M827" s="1">
+        <v>5.5555553399999997</v>
+      </c>
+      <c r="N827" s="1"/>
+      <c r="O827" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P827" s="1">
+        <v>4.3670886099999997</v>
+      </c>
+      <c r="Q827" s="1">
+        <v>0.83973328000000003</v>
+      </c>
+    </row>
+    <row r="828" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A828" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E828" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F828" s="1">
+        <v>10</v>
+      </c>
+      <c r="G828" s="1">
+        <v>9</v>
+      </c>
+      <c r="H828" s="1">
+        <v>90</v>
+      </c>
+      <c r="I828" s="1">
+        <v>4.3333334900000002</v>
+      </c>
+      <c r="J828" s="1">
+        <v>1</v>
+      </c>
+      <c r="K828" s="1">
+        <v>5</v>
+      </c>
+      <c r="L828" s="1">
+        <v>5</v>
+      </c>
+      <c r="M828" s="1">
+        <v>55.555557299999997</v>
+      </c>
+      <c r="N828" s="1"/>
+      <c r="O828" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P828" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q828" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="829" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A829" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E829" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F829" s="1">
+        <v>10</v>
+      </c>
+      <c r="G829" s="1">
+        <v>9</v>
+      </c>
+      <c r="H829" s="1">
+        <v>90</v>
+      </c>
+      <c r="I829" s="1">
+        <v>4.3333334900000002</v>
+      </c>
+      <c r="J829" s="1">
+        <v>1</v>
+      </c>
+      <c r="K829" s="1">
+        <v>4</v>
+      </c>
+      <c r="L829" s="1">
+        <v>3</v>
+      </c>
+      <c r="M829" s="1">
+        <v>33.3333321</v>
+      </c>
+      <c r="N829" s="1"/>
+      <c r="O829" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P829" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q829" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="830" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A830" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E830" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F830" s="1">
+        <v>10</v>
+      </c>
+      <c r="G830" s="1">
+        <v>9</v>
+      </c>
+      <c r="H830" s="1">
+        <v>90</v>
+      </c>
+      <c r="I830" s="1">
+        <v>4.3333334900000002</v>
+      </c>
+      <c r="J830" s="1">
+        <v>1</v>
+      </c>
+      <c r="K830" s="1">
+        <v>2</v>
+      </c>
+      <c r="L830" s="1">
+        <v>1</v>
+      </c>
+      <c r="M830" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N830" s="1"/>
+      <c r="O830" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P830" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q830" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="831" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A831" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E831" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F831" s="1">
+        <v>72</v>
+      </c>
+      <c r="G831" s="1">
+        <v>36</v>
+      </c>
+      <c r="H831" s="1">
+        <v>50</v>
+      </c>
+      <c r="I831" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J831" s="1">
+        <v>1.0939952100000001</v>
+      </c>
+      <c r="K831" s="1">
+        <v>5</v>
+      </c>
+      <c r="L831" s="1">
+        <v>13</v>
+      </c>
+      <c r="M831" s="1">
+        <v>36.111110699999998</v>
+      </c>
+      <c r="N831" s="1"/>
+      <c r="O831" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P831" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q831" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="832" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A832" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C832" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E832" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F832" s="1">
+        <v>72</v>
+      </c>
+      <c r="G832" s="1">
+        <v>36</v>
+      </c>
+      <c r="H832" s="1">
+        <v>50</v>
+      </c>
+      <c r="I832" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J832" s="1">
+        <v>1.0939952100000001</v>
+      </c>
+      <c r="K832" s="1">
+        <v>4</v>
+      </c>
+      <c r="L832" s="1">
+        <v>14</v>
+      </c>
+      <c r="M832" s="1">
+        <v>38.888889300000002</v>
+      </c>
+      <c r="N832" s="1"/>
+      <c r="O832" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P832" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q832" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="833" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A833" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E833" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F833" s="1">
+        <v>72</v>
+      </c>
+      <c r="G833" s="1">
+        <v>36</v>
+      </c>
+      <c r="H833" s="1">
+        <v>50</v>
+      </c>
+      <c r="I833" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J833" s="1">
+        <v>1.0939952100000001</v>
+      </c>
+      <c r="K833" s="1">
+        <v>3</v>
+      </c>
+      <c r="L833" s="1">
+        <v>4</v>
+      </c>
+      <c r="M833" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N833" s="1"/>
+      <c r="O833" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P833" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q833" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="834" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A834" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E834" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F834" s="1">
+        <v>72</v>
+      </c>
+      <c r="G834" s="1">
+        <v>36</v>
+      </c>
+      <c r="H834" s="1">
+        <v>50</v>
+      </c>
+      <c r="I834" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J834" s="1">
+        <v>1.0939952100000001</v>
+      </c>
+      <c r="K834" s="1">
+        <v>2</v>
+      </c>
+      <c r="L834" s="1">
+        <v>4</v>
+      </c>
+      <c r="M834" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N834" s="1"/>
+      <c r="O834" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P834" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q834" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="835" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A835" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C835" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E835" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F835" s="1">
+        <v>72</v>
+      </c>
+      <c r="G835" s="1">
+        <v>36</v>
+      </c>
+      <c r="H835" s="1">
+        <v>50</v>
+      </c>
+      <c r="I835" s="1">
+        <v>3.94444442</v>
+      </c>
+      <c r="J835" s="1">
+        <v>1.0939952100000001</v>
+      </c>
+      <c r="K835" s="1">
+        <v>1</v>
+      </c>
+      <c r="L835" s="1">
+        <v>1</v>
+      </c>
+      <c r="M835" s="1">
+        <v>2.7777776699999999</v>
+      </c>
+      <c r="N835" s="1"/>
+      <c r="O835" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P835" s="1">
+        <v>4.2125000000000004</v>
+      </c>
+      <c r="Q835" s="1">
+        <v>0.91381776000000003</v>
+      </c>
+    </row>
+    <row r="836" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A836" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C836" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D836" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E836" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F836" s="1">
+        <v>10</v>
+      </c>
+      <c r="G836" s="1">
+        <v>9</v>
+      </c>
+      <c r="H836" s="1">
+        <v>90</v>
+      </c>
+      <c r="I836" s="1">
+        <v>4.7777776699999999</v>
+      </c>
+      <c r="J836" s="1">
+        <v>0.44095856</v>
+      </c>
+      <c r="K836" s="1">
+        <v>5</v>
+      </c>
+      <c r="L836" s="1">
+        <v>7</v>
+      </c>
+      <c r="M836" s="1">
+        <v>77.777778600000005</v>
+      </c>
+      <c r="N836" s="1"/>
+      <c r="O836" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P836" s="1">
+        <v>4.5379746799999996</v>
+      </c>
+      <c r="Q836" s="1">
+        <v>0.77899229000000003</v>
+      </c>
+    </row>
+    <row r="837" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A837" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C837" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E837" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F837" s="1">
+        <v>10</v>
+      </c>
+      <c r="G837" s="1">
+        <v>9</v>
+      </c>
+      <c r="H837" s="1">
+        <v>90</v>
+      </c>
+      <c r="I837" s="1">
+        <v>4.7777776699999999</v>
+      </c>
+      <c r="J837" s="1">
+        <v>0.44095856</v>
+      </c>
+      <c r="K837" s="1">
+        <v>4</v>
+      </c>
+      <c r="L837" s="1">
+        <v>2</v>
+      </c>
+      <c r="M837" s="1">
+        <v>22.222221399999999</v>
+      </c>
+      <c r="N837" s="1"/>
+      <c r="O837" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P837" s="1">
+        <v>4.5379746799999996</v>
+      </c>
+      <c r="Q837" s="1">
+        <v>0.77899229000000003</v>
+      </c>
+    </row>
+    <row r="838" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A838" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E838" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F838" s="1">
+        <v>72</v>
+      </c>
+      <c r="G838" s="1">
+        <v>34</v>
+      </c>
+      <c r="H838" s="1">
+        <v>47.222221400000002</v>
+      </c>
+      <c r="I838" s="1">
+        <v>4.1176471699999997</v>
+      </c>
+      <c r="J838" s="1">
+        <v>1.17459738</v>
+      </c>
+      <c r="K838" s="1">
+        <v>5</v>
+      </c>
+      <c r="L838" s="1">
+        <v>16</v>
+      </c>
+      <c r="M838" s="1">
+        <v>47.058822599999999</v>
+      </c>
+      <c r="N838" s="1"/>
+      <c r="O838" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P838" s="1">
+        <v>4.5379746799999996</v>
+      </c>
+      <c r="Q838" s="1">
+        <v>0.77899229000000003</v>
+      </c>
+    </row>
+    <row r="839" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A839" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C839" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E839" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F839" s="1">
+        <v>72</v>
+      </c>
+      <c r="G839" s="1">
+        <v>34</v>
+      </c>
+      <c r="H839" s="1">
+        <v>47.222221400000002</v>
+      </c>
+      <c r="I839" s="1">
+        <v>4.1176471699999997</v>
+      </c>
+      <c r="J839" s="1">
+        <v>1.17459738</v>
+      </c>
+      <c r="K839" s="1">
+        <v>4</v>
+      </c>
+      <c r="L839" s="1">
+        <v>12</v>
+      </c>
+      <c r="M839" s="1">
+        <v>35.294117</v>
+      </c>
+      <c r="N839" s="1"/>
+      <c r="O839" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P839" s="1">
+        <v>4.5379746799999996</v>
+      </c>
+      <c r="Q839" s="1">
+        <v>0.77899229000000003</v>
+      </c>
+    </row>
+    <row r="840" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A840" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E840" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F840" s="1">
+        <v>72</v>
+      </c>
+      <c r="G840" s="1">
+        <v>34</v>
+      </c>
+      <c r="H840" s="1">
+        <v>47.222221400000002</v>
+      </c>
+      <c r="I840" s="1">
+        <v>4.1176471699999997</v>
+      </c>
+      <c r="J840" s="1">
+        <v>1.17459738</v>
+      </c>
+      <c r="K840" s="1">
+        <v>3</v>
+      </c>
+      <c r="L840" s="1">
+        <v>3</v>
+      </c>
+      <c r="M840" s="1">
+        <v>8.8235292399999992</v>
+      </c>
+      <c r="N840" s="1"/>
+      <c r="O840" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P840" s="1">
+        <v>4.5379746799999996</v>
+      </c>
+      <c r="Q840" s="1">
+        <v>0.77899229000000003</v>
+      </c>
+    </row>
+    <row r="841" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A841" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E841" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F841" s="1">
+        <v>72</v>
+      </c>
+      <c r="G841" s="1">
+        <v>34</v>
+      </c>
+      <c r="H841" s="1">
+        <v>47.222221400000002</v>
+      </c>
+      <c r="I841" s="1">
+        <v>4.1176471699999997</v>
+      </c>
+      <c r="J841" s="1">
+        <v>1.17459738</v>
+      </c>
+      <c r="K841" s="1">
+        <v>1</v>
+      </c>
+      <c r="L841" s="1">
+        <v>3</v>
+      </c>
+      <c r="M841" s="1">
+        <v>8.8235292399999992</v>
+      </c>
+      <c r="N841" s="1"/>
+      <c r="O841" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P841" s="1">
+        <v>4.5379746799999996</v>
+      </c>
+      <c r="Q841" s="1">
+        <v>0.77899229000000003</v>
+      </c>
+    </row>
+    <row r="842" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A842" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E842" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F842" s="1">
+        <v>10</v>
+      </c>
+      <c r="G842" s="1">
+        <v>9</v>
+      </c>
+      <c r="H842" s="1">
+        <v>90</v>
+      </c>
+      <c r="I842" s="1">
+        <v>4.8888888399999999</v>
+      </c>
+      <c r="J842" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K842" s="1">
+        <v>5</v>
+      </c>
+      <c r="L842" s="1">
+        <v>8</v>
+      </c>
+      <c r="M842" s="1">
+        <v>88.888885500000001</v>
+      </c>
+      <c r="N842" s="1"/>
+      <c r="O842" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P842" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q842" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="843" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A843" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D843" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E843" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F843" s="1">
+        <v>10</v>
+      </c>
+      <c r="G843" s="1">
+        <v>9</v>
+      </c>
+      <c r="H843" s="1">
+        <v>90</v>
+      </c>
+      <c r="I843" s="1">
+        <v>4.8888888399999999</v>
+      </c>
+      <c r="J843" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K843" s="1">
+        <v>4</v>
+      </c>
+      <c r="L843" s="1">
+        <v>1</v>
+      </c>
+      <c r="M843" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N843" s="1"/>
+      <c r="O843" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P843" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q843" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="844" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A844" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E844" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F844" s="1">
+        <v>72</v>
+      </c>
+      <c r="G844" s="1">
+        <v>36</v>
+      </c>
+      <c r="H844" s="1">
+        <v>50</v>
+      </c>
+      <c r="I844" s="1">
+        <v>4.1666665099999998</v>
+      </c>
+      <c r="J844" s="1">
+        <v>1.1832159799999999</v>
+      </c>
+      <c r="K844" s="1">
+        <v>5</v>
+      </c>
+      <c r="L844" s="1">
+        <v>18</v>
+      </c>
+      <c r="M844" s="1">
+        <v>50</v>
+      </c>
+      <c r="N844" s="1"/>
+      <c r="O844" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P844" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q844" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="845" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A845" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C845" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E845" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F845" s="1">
+        <v>72</v>
+      </c>
+      <c r="G845" s="1">
+        <v>36</v>
+      </c>
+      <c r="H845" s="1">
+        <v>50</v>
+      </c>
+      <c r="I845" s="1">
+        <v>4.1666665099999998</v>
+      </c>
+      <c r="J845" s="1">
+        <v>1.1832159799999999</v>
+      </c>
+      <c r="K845" s="1">
+        <v>4</v>
+      </c>
+      <c r="L845" s="1">
+        <v>13</v>
+      </c>
+      <c r="M845" s="1">
+        <v>36.111110699999998</v>
+      </c>
+      <c r="N845" s="1"/>
+      <c r="O845" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P845" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q845" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="846" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A846" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D846" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E846" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F846" s="1">
+        <v>72</v>
+      </c>
+      <c r="G846" s="1">
+        <v>36</v>
+      </c>
+      <c r="H846" s="1">
+        <v>50</v>
+      </c>
+      <c r="I846" s="1">
+        <v>4.1666665099999998</v>
+      </c>
+      <c r="J846" s="1">
+        <v>1.1832159799999999</v>
+      </c>
+      <c r="K846" s="1">
+        <v>3</v>
+      </c>
+      <c r="L846" s="1">
+        <v>1</v>
+      </c>
+      <c r="M846" s="1">
+        <v>2.7777776699999999</v>
+      </c>
+      <c r="N846" s="1"/>
+      <c r="O846" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P846" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q846" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="847" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A847" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C847" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D847" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E847" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F847" s="1">
+        <v>72</v>
+      </c>
+      <c r="G847" s="1">
+        <v>36</v>
+      </c>
+      <c r="H847" s="1">
+        <v>50</v>
+      </c>
+      <c r="I847" s="1">
+        <v>4.1666665099999998</v>
+      </c>
+      <c r="J847" s="1">
+        <v>1.1832159799999999</v>
+      </c>
+      <c r="K847" s="1">
+        <v>2</v>
+      </c>
+      <c r="L847" s="1">
+        <v>1</v>
+      </c>
+      <c r="M847" s="1">
+        <v>2.7777776699999999</v>
+      </c>
+      <c r="N847" s="1"/>
+      <c r="O847" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P847" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q847" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="848" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A848" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B848" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D848" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E848" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F848" s="1">
+        <v>72</v>
+      </c>
+      <c r="G848" s="1">
+        <v>36</v>
+      </c>
+      <c r="H848" s="1">
+        <v>50</v>
+      </c>
+      <c r="I848" s="1">
+        <v>4.1666665099999998</v>
+      </c>
+      <c r="J848" s="1">
+        <v>1.1832159799999999</v>
+      </c>
+      <c r="K848" s="1">
+        <v>1</v>
+      </c>
+      <c r="L848" s="1">
+        <v>3</v>
+      </c>
+      <c r="M848" s="1">
+        <v>8.3333330199999995</v>
+      </c>
+      <c r="N848" s="1"/>
+      <c r="O848" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P848" s="1">
+        <v>4.5802919700000002</v>
+      </c>
+      <c r="Q848" s="1">
+        <v>0.70771152000000004</v>
+      </c>
+    </row>
+    <row r="849" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A849" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D849" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E849" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F849" s="1">
+        <v>10</v>
+      </c>
+      <c r="G849" s="1">
+        <v>9</v>
+      </c>
+      <c r="H849" s="1">
+        <v>90</v>
+      </c>
+      <c r="I849" s="1">
+        <v>4.8888888399999999</v>
+      </c>
+      <c r="J849" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K849" s="1">
+        <v>5</v>
+      </c>
+      <c r="L849" s="1">
+        <v>8</v>
+      </c>
+      <c r="M849" s="1">
+        <v>88.888885500000001</v>
+      </c>
+      <c r="N849" s="1"/>
+      <c r="O849" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P849" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q849" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="850" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A850" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B850" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D850" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E850" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F850" s="1">
+        <v>10</v>
+      </c>
+      <c r="G850" s="1">
+        <v>9</v>
+      </c>
+      <c r="H850" s="1">
+        <v>90</v>
+      </c>
+      <c r="I850" s="1">
+        <v>4.8888888399999999</v>
+      </c>
+      <c r="J850" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K850" s="1">
+        <v>4</v>
+      </c>
+      <c r="L850" s="1">
+        <v>1</v>
+      </c>
+      <c r="M850" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N850" s="1"/>
+      <c r="O850" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P850" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q850" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="851" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A851" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D851" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E851" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F851" s="1">
+        <v>72</v>
+      </c>
+      <c r="G851" s="1">
+        <v>35</v>
+      </c>
+      <c r="H851" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I851" s="1">
+        <v>4.1142859500000002</v>
+      </c>
+      <c r="J851" s="1">
+        <v>1.3009369399999999</v>
+      </c>
+      <c r="K851" s="1">
+        <v>5</v>
+      </c>
+      <c r="L851" s="1">
+        <v>20</v>
+      </c>
+      <c r="M851" s="1">
+        <v>57.142856600000002</v>
+      </c>
+      <c r="N851" s="1"/>
+      <c r="O851" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P851" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q851" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="852" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A852" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B852" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C852" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D852" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E852" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F852" s="1">
+        <v>72</v>
+      </c>
+      <c r="G852" s="1">
+        <v>35</v>
+      </c>
+      <c r="H852" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I852" s="1">
+        <v>4.1142859500000002</v>
+      </c>
+      <c r="J852" s="1">
+        <v>1.3009369399999999</v>
+      </c>
+      <c r="K852" s="1">
+        <v>4</v>
+      </c>
+      <c r="L852" s="1">
+        <v>7</v>
+      </c>
+      <c r="M852" s="1">
+        <v>20</v>
+      </c>
+      <c r="N852" s="1"/>
+      <c r="O852" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P852" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q852" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="853" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A853" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B853" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C853" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D853" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E853" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F853" s="1">
+        <v>72</v>
+      </c>
+      <c r="G853" s="1">
+        <v>35</v>
+      </c>
+      <c r="H853" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I853" s="1">
+        <v>4.1142859500000002</v>
+      </c>
+      <c r="J853" s="1">
+        <v>1.3009369399999999</v>
+      </c>
+      <c r="K853" s="1">
+        <v>3</v>
+      </c>
+      <c r="L853" s="1">
+        <v>3</v>
+      </c>
+      <c r="M853" s="1">
+        <v>8.5714283000000009</v>
+      </c>
+      <c r="N853" s="1"/>
+      <c r="O853" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P853" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q853" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="854" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A854" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B854" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C854" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D854" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E854" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F854" s="1">
+        <v>72</v>
+      </c>
+      <c r="G854" s="1">
+        <v>35</v>
+      </c>
+      <c r="H854" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I854" s="1">
+        <v>4.1142859500000002</v>
+      </c>
+      <c r="J854" s="1">
+        <v>1.3009369399999999</v>
+      </c>
+      <c r="K854" s="1">
+        <v>2</v>
+      </c>
+      <c r="L854" s="1">
+        <v>2</v>
+      </c>
+      <c r="M854" s="1">
+        <v>5.7142858499999996</v>
+      </c>
+      <c r="N854" s="1"/>
+      <c r="O854" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P854" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q854" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="855" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A855" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B855" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C855" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D855" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E855" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F855" s="1">
+        <v>72</v>
+      </c>
+      <c r="G855" s="1">
+        <v>35</v>
+      </c>
+      <c r="H855" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I855" s="1">
+        <v>4.1142859500000002</v>
+      </c>
+      <c r="J855" s="1">
+        <v>1.3009369399999999</v>
+      </c>
+      <c r="K855" s="1">
+        <v>1</v>
+      </c>
+      <c r="L855" s="1">
+        <v>3</v>
+      </c>
+      <c r="M855" s="1">
+        <v>8.5714283000000009</v>
+      </c>
+      <c r="N855" s="1"/>
+      <c r="O855" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P855" s="1">
+        <v>4.5677655699999997</v>
+      </c>
+      <c r="Q855" s="1">
+        <v>0.74507288000000005</v>
+      </c>
+    </row>
+    <row r="856" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A856" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B856" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C856" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D856" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E856" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F856" s="1">
+        <v>10</v>
+      </c>
+      <c r="G856" s="1">
+        <v>9</v>
+      </c>
+      <c r="H856" s="1">
+        <v>90</v>
+      </c>
+      <c r="I856" s="1">
+        <v>5</v>
+      </c>
+      <c r="J856" s="1">
+        <v>0</v>
+      </c>
+      <c r="K856" s="1">
+        <v>5</v>
+      </c>
+      <c r="L856" s="1">
+        <v>9</v>
+      </c>
+      <c r="M856" s="1">
+        <v>100</v>
+      </c>
+      <c r="N856" s="1"/>
+      <c r="O856" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P856" s="1">
+        <v>4.6642335800000003</v>
+      </c>
+      <c r="Q856" s="1">
+        <v>0.62049692999999995</v>
+      </c>
+    </row>
+    <row r="857" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A857" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B857" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C857" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D857" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E857" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F857" s="1">
+        <v>72</v>
+      </c>
+      <c r="G857" s="1">
+        <v>36</v>
+      </c>
+      <c r="H857" s="1">
+        <v>50</v>
+      </c>
+      <c r="I857" s="1">
+        <v>4.4166665099999998</v>
+      </c>
+      <c r="J857" s="1">
+        <v>0.99642217</v>
+      </c>
+      <c r="K857" s="1">
+        <v>5</v>
+      </c>
+      <c r="L857" s="1">
+        <v>22</v>
+      </c>
+      <c r="M857" s="1">
+        <v>61.111110699999998</v>
+      </c>
+      <c r="N857" s="1"/>
+      <c r="O857" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P857" s="1">
+        <v>4.6642335800000003</v>
+      </c>
+      <c r="Q857" s="1">
+        <v>0.62049692999999995</v>
+      </c>
+    </row>
+    <row r="858" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A858" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B858" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C858" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D858" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E858" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F858" s="1">
+        <v>72</v>
+      </c>
+      <c r="G858" s="1">
+        <v>36</v>
+      </c>
+      <c r="H858" s="1">
+        <v>50</v>
+      </c>
+      <c r="I858" s="1">
+        <v>4.4166665099999998</v>
+      </c>
+      <c r="J858" s="1">
+        <v>0.99642217</v>
+      </c>
+      <c r="K858" s="1">
+        <v>4</v>
+      </c>
+      <c r="L858" s="1">
+        <v>11</v>
+      </c>
+      <c r="M858" s="1">
+        <v>30.555555300000002</v>
+      </c>
+      <c r="N858" s="1"/>
+      <c r="O858" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P858" s="1">
+        <v>4.6642335800000003</v>
+      </c>
+      <c r="Q858" s="1">
+        <v>0.62049692999999995</v>
+      </c>
+    </row>
+    <row r="859" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A859" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D859" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E859" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F859" s="1">
+        <v>72</v>
+      </c>
+      <c r="G859" s="1">
+        <v>36</v>
+      </c>
+      <c r="H859" s="1">
+        <v>50</v>
+      </c>
+      <c r="I859" s="1">
+        <v>4.4166665099999998</v>
+      </c>
+      <c r="J859" s="1">
+        <v>0.99642217</v>
+      </c>
+      <c r="K859" s="1">
+        <v>3</v>
+      </c>
+      <c r="L859" s="1">
+        <v>1</v>
+      </c>
+      <c r="M859" s="1">
+        <v>2.7777776699999999</v>
+      </c>
+      <c r="N859" s="1"/>
+      <c r="O859" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P859" s="1">
+        <v>4.6642335800000003</v>
+      </c>
+      <c r="Q859" s="1">
+        <v>0.62049692999999995</v>
+      </c>
+    </row>
+    <row r="860" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A860" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B860" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C860" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D860" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E860" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F860" s="1">
+        <v>72</v>
+      </c>
+      <c r="G860" s="1">
+        <v>36</v>
+      </c>
+      <c r="H860" s="1">
+        <v>50</v>
+      </c>
+      <c r="I860" s="1">
+        <v>4.4166665099999998</v>
+      </c>
+      <c r="J860" s="1">
+        <v>0.99642217</v>
+      </c>
+      <c r="K860" s="1">
+        <v>1</v>
+      </c>
+      <c r="L860" s="1">
+        <v>2</v>
+      </c>
+      <c r="M860" s="1">
+        <v>5.5555553399999997</v>
+      </c>
+      <c r="N860" s="1"/>
+      <c r="O860" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P860" s="1">
+        <v>4.6642335800000003</v>
+      </c>
+      <c r="Q860" s="1">
+        <v>0.62049692999999995</v>
+      </c>
+    </row>
+    <row r="861" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A861" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C861" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D861" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E861" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F861" s="1">
+        <v>10</v>
+      </c>
+      <c r="G861" s="1">
+        <v>9</v>
+      </c>
+      <c r="H861" s="1">
+        <v>90</v>
+      </c>
+      <c r="I861" s="1">
+        <v>4.8888888399999999</v>
+      </c>
+      <c r="J861" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K861" s="1">
+        <v>5</v>
+      </c>
+      <c r="L861" s="1">
+        <v>8</v>
+      </c>
+      <c r="M861" s="1">
+        <v>88.888885500000001</v>
+      </c>
+      <c r="N861" s="1"/>
+      <c r="O861" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P861" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q861" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="862" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A862" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D862" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E862" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F862" s="1">
+        <v>10</v>
+      </c>
+      <c r="G862" s="1">
+        <v>9</v>
+      </c>
+      <c r="H862" s="1">
+        <v>90</v>
+      </c>
+      <c r="I862" s="1">
+        <v>4.8888888399999999</v>
+      </c>
+      <c r="J862" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K862" s="1">
+        <v>4</v>
+      </c>
+      <c r="L862" s="1">
+        <v>1</v>
+      </c>
+      <c r="M862" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N862" s="1"/>
+      <c r="O862" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P862" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q862" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="863" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A863" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D863" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E863" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F863" s="1">
+        <v>72</v>
+      </c>
+      <c r="G863" s="1">
+        <v>36</v>
+      </c>
+      <c r="H863" s="1">
+        <v>50</v>
+      </c>
+      <c r="I863" s="1">
+        <v>4.2777776699999999</v>
+      </c>
+      <c r="J863" s="1">
+        <v>1.05860043</v>
+      </c>
+      <c r="K863" s="1">
+        <v>5</v>
+      </c>
+      <c r="L863" s="1">
+        <v>19</v>
+      </c>
+      <c r="M863" s="1">
+        <v>52.777778599999998</v>
+      </c>
+      <c r="N863" s="1"/>
+      <c r="O863" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P863" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q863" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="864" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A864" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D864" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E864" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F864" s="1">
+        <v>72</v>
+      </c>
+      <c r="G864" s="1">
+        <v>36</v>
+      </c>
+      <c r="H864" s="1">
+        <v>50</v>
+      </c>
+      <c r="I864" s="1">
+        <v>4.2777776699999999</v>
+      </c>
+      <c r="J864" s="1">
+        <v>1.05860043</v>
+      </c>
+      <c r="K864" s="1">
+        <v>4</v>
+      </c>
+      <c r="L864" s="1">
+        <v>13</v>
+      </c>
+      <c r="M864" s="1">
+        <v>36.111110699999998</v>
+      </c>
+      <c r="N864" s="1"/>
+      <c r="O864" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P864" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q864" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="865" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A865" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E865" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F865" s="1">
+        <v>72</v>
+      </c>
+      <c r="G865" s="1">
+        <v>36</v>
+      </c>
+      <c r="H865" s="1">
+        <v>50</v>
+      </c>
+      <c r="I865" s="1">
+        <v>4.2777776699999999</v>
+      </c>
+      <c r="J865" s="1">
+        <v>1.05860043</v>
+      </c>
+      <c r="K865" s="1">
+        <v>3</v>
+      </c>
+      <c r="L865" s="1">
+        <v>1</v>
+      </c>
+      <c r="M865" s="1">
+        <v>2.7777776699999999</v>
+      </c>
+      <c r="N865" s="1"/>
+      <c r="O865" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P865" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q865" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="866" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A866" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D866" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E866" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F866" s="1">
+        <v>72</v>
+      </c>
+      <c r="G866" s="1">
+        <v>36</v>
+      </c>
+      <c r="H866" s="1">
+        <v>50</v>
+      </c>
+      <c r="I866" s="1">
+        <v>4.2777776699999999</v>
+      </c>
+      <c r="J866" s="1">
+        <v>1.05860043</v>
+      </c>
+      <c r="K866" s="1">
+        <v>2</v>
+      </c>
+      <c r="L866" s="1">
+        <v>1</v>
+      </c>
+      <c r="M866" s="1">
+        <v>2.7777776699999999</v>
+      </c>
+      <c r="N866" s="1"/>
+      <c r="O866" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P866" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q866" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="867" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A867" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E867" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F867" s="1">
+        <v>72</v>
+      </c>
+      <c r="G867" s="1">
+        <v>36</v>
+      </c>
+      <c r="H867" s="1">
+        <v>50</v>
+      </c>
+      <c r="I867" s="1">
+        <v>4.2777776699999999</v>
+      </c>
+      <c r="J867" s="1">
+        <v>1.05860043</v>
+      </c>
+      <c r="K867" s="1">
+        <v>1</v>
+      </c>
+      <c r="L867" s="1">
+        <v>2</v>
+      </c>
+      <c r="M867" s="1">
+        <v>5.5555553399999997</v>
+      </c>
+      <c r="N867" s="1"/>
+      <c r="O867" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P867" s="1">
+        <v>4.5948905099999999</v>
+      </c>
+      <c r="Q867" s="1">
+        <v>0.67404211000000003</v>
+      </c>
+    </row>
+    <row r="868" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A868" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D868" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E868" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F868" s="1">
+        <v>10</v>
+      </c>
+      <c r="G868" s="1">
+        <v>9</v>
+      </c>
+      <c r="H868" s="1">
+        <v>90</v>
+      </c>
+      <c r="I868" s="1">
+        <v>4.5555553399999997</v>
+      </c>
+      <c r="J868" s="1">
+        <v>0.72648316999999996</v>
+      </c>
+      <c r="K868" s="1">
+        <v>5</v>
+      </c>
+      <c r="L868" s="1">
+        <v>6</v>
+      </c>
+      <c r="M868" s="1">
+        <v>66.666664100000006</v>
+      </c>
+      <c r="N868" s="1"/>
+      <c r="O868" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P868" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q868" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="869" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A869" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C869" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D869" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E869" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F869" s="1">
+        <v>10</v>
+      </c>
+      <c r="G869" s="1">
+        <v>9</v>
+      </c>
+      <c r="H869" s="1">
+        <v>90</v>
+      </c>
+      <c r="I869" s="1">
+        <v>4.5555553399999997</v>
+      </c>
+      <c r="J869" s="1">
+        <v>0.72648316999999996</v>
+      </c>
+      <c r="K869" s="1">
+        <v>4</v>
+      </c>
+      <c r="L869" s="1">
+        <v>2</v>
+      </c>
+      <c r="M869" s="1">
+        <v>22.222221399999999</v>
+      </c>
+      <c r="N869" s="1"/>
+      <c r="O869" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P869" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q869" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="870" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A870" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C870" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D870" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E870" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F870" s="1">
+        <v>10</v>
+      </c>
+      <c r="G870" s="1">
+        <v>9</v>
+      </c>
+      <c r="H870" s="1">
+        <v>90</v>
+      </c>
+      <c r="I870" s="1">
+        <v>4.5555553399999997</v>
+      </c>
+      <c r="J870" s="1">
+        <v>0.72648316999999996</v>
+      </c>
+      <c r="K870" s="1">
+        <v>3</v>
+      </c>
+      <c r="L870" s="1">
+        <v>1</v>
+      </c>
+      <c r="M870" s="1">
+        <v>11.111110699999999</v>
+      </c>
+      <c r="N870" s="1"/>
+      <c r="O870" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P870" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q870" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="871" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A871" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D871" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E871" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F871" s="1">
+        <v>72</v>
+      </c>
+      <c r="G871" s="1">
+        <v>35</v>
+      </c>
+      <c r="H871" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I871" s="1">
+        <v>4.2857141500000004</v>
+      </c>
+      <c r="J871" s="1">
+        <v>1.01666784</v>
+      </c>
+      <c r="K871" s="1">
+        <v>5</v>
+      </c>
+      <c r="L871" s="1">
+        <v>18</v>
+      </c>
+      <c r="M871" s="1">
+        <v>51.428569799999998</v>
+      </c>
+      <c r="N871" s="1"/>
+      <c r="O871" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P871" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q871" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="872" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A872" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B872" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C872" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E872" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F872" s="1">
+        <v>72</v>
+      </c>
+      <c r="G872" s="1">
+        <v>35</v>
+      </c>
+      <c r="H872" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I872" s="1">
+        <v>4.2857141500000004</v>
+      </c>
+      <c r="J872" s="1">
+        <v>1.01666784</v>
+      </c>
+      <c r="K872" s="1">
+        <v>4</v>
+      </c>
+      <c r="L872" s="1">
+        <v>13</v>
+      </c>
+      <c r="M872" s="1">
+        <v>37.142856600000002</v>
+      </c>
+      <c r="N872" s="1"/>
+      <c r="O872" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P872" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q872" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="873" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A873" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B873" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C873" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D873" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E873" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F873" s="1">
+        <v>72</v>
+      </c>
+      <c r="G873" s="1">
+        <v>35</v>
+      </c>
+      <c r="H873" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I873" s="1">
+        <v>4.2857141500000004</v>
+      </c>
+      <c r="J873" s="1">
+        <v>1.01666784</v>
+      </c>
+      <c r="K873" s="1">
+        <v>3</v>
+      </c>
+      <c r="L873" s="1">
+        <v>2</v>
+      </c>
+      <c r="M873" s="1">
+        <v>5.7142858499999996</v>
+      </c>
+      <c r="N873" s="1"/>
+      <c r="O873" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P873" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q873" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="874" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A874" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B874" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C874" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D874" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E874" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F874" s="1">
+        <v>72</v>
+      </c>
+      <c r="G874" s="1">
+        <v>35</v>
+      </c>
+      <c r="H874" s="1">
+        <v>48.611110699999998</v>
+      </c>
+      <c r="I874" s="1">
+        <v>4.2857141500000004</v>
+      </c>
+      <c r="J874" s="1">
+        <v>1.01666784</v>
+      </c>
+      <c r="K874" s="1">
+        <v>1</v>
+      </c>
+      <c r="L874" s="1">
+        <v>2</v>
+      </c>
+      <c r="M874" s="1">
+        <v>5.7142858499999996</v>
+      </c>
+      <c r="N874" s="1"/>
+      <c r="O874" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P874" s="1">
+        <v>4.5567765600000003</v>
+      </c>
+      <c r="Q874" s="1">
+        <v>0.70546699999999996</v>
+      </c>
+    </row>
+    <row r="875" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A875" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B875" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D875" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E875" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F875" s="1">
+        <v>10</v>
+      </c>
+      <c r="G875" s="1">
+        <v>9</v>
+      </c>
+      <c r="H875" s="1">
+        <v>90</v>
+      </c>
+      <c r="I875" s="1">
+        <v>5</v>
+      </c>
+      <c r="J875" s="1">
+        <v>0</v>
+      </c>
+      <c r="K875" s="1">
+        <v>5</v>
+      </c>
+      <c r="L875" s="1">
+        <v>9</v>
+      </c>
+      <c r="M875" s="1">
+        <v>100</v>
+      </c>
+      <c r="N875" s="1"/>
+      <c r="O875" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P875" s="1">
+        <v>4.6327272700000002</v>
+      </c>
+      <c r="Q875" s="1">
+        <v>0.61580597000000004</v>
+      </c>
+    </row>
+    <row r="876" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A876" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B876" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C876" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D876" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E876" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F876" s="1">
+        <v>72</v>
+      </c>
+      <c r="G876" s="1">
+        <v>36</v>
+      </c>
+      <c r="H876" s="1">
+        <v>50</v>
+      </c>
+      <c r="I876" s="1">
+        <v>4.3055553399999997</v>
+      </c>
+      <c r="J876" s="1">
+        <v>1.00908566</v>
+      </c>
+      <c r="K876" s="1">
+        <v>5</v>
+      </c>
+      <c r="L876" s="1">
+        <v>19</v>
+      </c>
+      <c r="M876" s="1">
+        <v>52.777778599999998</v>
+      </c>
+      <c r="N876" s="1"/>
+      <c r="O876" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P876" s="1">
+        <v>4.6327272700000002</v>
+      </c>
+      <c r="Q876" s="1">
+        <v>0.61580597000000004</v>
+      </c>
+    </row>
+    <row r="877" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A877" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B877" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C877" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D877" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E877" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F877" s="1">
+        <v>72</v>
+      </c>
+      <c r="G877" s="1">
+        <v>36</v>
+      </c>
+      <c r="H877" s="1">
+        <v>50</v>
+      </c>
+      <c r="I877" s="1">
+        <v>4.3055553399999997</v>
+      </c>
+      <c r="J877" s="1">
+        <v>1.00908566</v>
+      </c>
+      <c r="K877" s="1">
+        <v>4</v>
+      </c>
+      <c r="L877" s="1">
+        <v>13</v>
+      </c>
+      <c r="M877" s="1">
+        <v>36.111110699999998</v>
+      </c>
+      <c r="N877" s="1"/>
+      <c r="O877" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P877" s="1">
+        <v>4.6327272700000002</v>
+      </c>
+      <c r="Q877" s="1">
+        <v>0.61580597000000004</v>
+      </c>
+    </row>
+    <row r="878" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A878" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B878" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C878" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D878" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E878" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F878" s="1">
+        <v>72</v>
+      </c>
+      <c r="G878" s="1">
+        <v>36</v>
+      </c>
+      <c r="H878" s="1">
+        <v>50</v>
+      </c>
+      <c r="I878" s="1">
+        <v>4.3055553399999997</v>
+      </c>
+      <c r="J878" s="1">
+        <v>1.00908566</v>
+      </c>
+      <c r="K878" s="1">
+        <v>3</v>
+      </c>
+      <c r="L878" s="1">
+        <v>2</v>
+      </c>
+      <c r="M878" s="1">
+        <v>5.5555553399999997</v>
+      </c>
+      <c r="N878" s="1"/>
+      <c r="O878" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P878" s="1">
+        <v>4.6327272700000002</v>
+      </c>
+      <c r="Q878" s="1">
+        <v>0.61580597000000004</v>
+      </c>
+    </row>
+    <row r="879" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A879" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B879" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C879" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D879" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E879" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F879" s="1">
+        <v>72</v>
+      </c>
+      <c r="G879" s="1">
+        <v>36</v>
+      </c>
+      <c r="H879" s="1">
+        <v>50</v>
+      </c>
+      <c r="I879" s="1">
+        <v>4.3055553399999997</v>
+      </c>
+      <c r="J879" s="1">
+        <v>1.00908566</v>
+      </c>
+      <c r="K879" s="1">
+        <v>1</v>
+      </c>
+      <c r="L879" s="1">
+        <v>2</v>
+      </c>
+      <c r="M879" s="1">
+        <v>5.5555553399999997</v>
+      </c>
+      <c r="N879" s="1"/>
+      <c r="O879" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P879" s="1">
+        <v>4.6327272700000002</v>
+      </c>
+      <c r="Q879" s="1">
+        <v>0.61580597000000004</v>
+      </c>
+    </row>
+    <row r="880" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A880" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B880" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C880" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D880" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E880" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F880" s="1">
+        <v>17</v>
+      </c>
+      <c r="G880" s="1">
+        <v>15</v>
+      </c>
+      <c r="H880" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I880" s="1">
+        <v>4.2666668899999998</v>
+      </c>
+      <c r="J880" s="1">
+        <v>0.59361684000000003</v>
+      </c>
+      <c r="K880" s="1">
+        <v>3</v>
+      </c>
+      <c r="L880" s="1">
+        <v>1</v>
+      </c>
+      <c r="M880" s="1">
+        <v>6.6666665099999998</v>
+      </c>
+      <c r="N880" s="1"/>
+      <c r="O880" s="1"/>
+      <c r="P880" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q880" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A881" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B881" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C881" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D881" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E881" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F881" s="1">
+        <v>17</v>
+      </c>
+      <c r="G881" s="1">
+        <v>15</v>
+      </c>
+      <c r="H881" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I881" s="1">
+        <v>4.2666668899999998</v>
+      </c>
+      <c r="J881" s="1">
+        <v>0.59361684000000003</v>
+      </c>
+      <c r="K881" s="1">
+        <v>4</v>
+      </c>
+      <c r="L881" s="1">
+        <v>9</v>
+      </c>
+      <c r="M881" s="1">
+        <v>60</v>
+      </c>
+      <c r="N881" s="1"/>
+      <c r="O881" s="1"/>
+      <c r="P881" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q881" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A882" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B882" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C882" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D882" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E882" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F882" s="1">
+        <v>17</v>
+      </c>
+      <c r="G882" s="1">
+        <v>15</v>
+      </c>
+      <c r="H882" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I882" s="1">
+        <v>4.2666668899999998</v>
+      </c>
+      <c r="J882" s="1">
+        <v>0.59361684000000003</v>
+      </c>
+      <c r="K882" s="1">
+        <v>5</v>
+      </c>
+      <c r="L882" s="1">
+        <v>5</v>
+      </c>
+      <c r="M882" s="1">
+        <v>33.3333321</v>
+      </c>
+      <c r="N882" s="1"/>
+      <c r="O882" s="1"/>
+      <c r="P882" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q882" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A883" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B883" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C883" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D883" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E883" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F883" s="1">
+        <v>17</v>
+      </c>
+      <c r="G883" s="1">
+        <v>15</v>
+      </c>
+      <c r="H883" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I883" s="1">
+        <v>4.4000000999999997</v>
+      </c>
+      <c r="J883" s="1">
+        <v>0.73678838999999996</v>
+      </c>
+      <c r="K883" s="1">
+        <v>3</v>
+      </c>
+      <c r="L883" s="1">
+        <v>2</v>
+      </c>
+      <c r="M883" s="1">
+        <v>13.333333</v>
+      </c>
+      <c r="N883" s="1"/>
+      <c r="O883" s="1"/>
+      <c r="P883" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q883" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A884" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B884" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C884" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D884" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E884" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F884" s="1">
+        <v>17</v>
+      </c>
+      <c r="G884" s="1">
+        <v>15</v>
+      </c>
+      <c r="H884" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I884" s="1">
+        <v>4.4000000999999997</v>
+      </c>
+      <c r="J884" s="1">
+        <v>0.73678838999999996</v>
+      </c>
+      <c r="K884" s="1">
+        <v>4</v>
+      </c>
+      <c r="L884" s="1">
+        <v>5</v>
+      </c>
+      <c r="M884" s="1">
+        <v>33.3333321</v>
+      </c>
+      <c r="N884" s="1"/>
+      <c r="O884" s="1"/>
+      <c r="P884" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q884" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A885" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B885" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C885" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D885" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E885" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F885" s="1">
+        <v>17</v>
+      </c>
+      <c r="G885" s="1">
+        <v>15</v>
+      </c>
+      <c r="H885" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I885" s="1">
+        <v>4.4000000999999997</v>
+      </c>
+      <c r="J885" s="1">
+        <v>0.73678838999999996</v>
+      </c>
+      <c r="K885" s="1">
+        <v>5</v>
+      </c>
+      <c r="L885" s="1">
+        <v>8</v>
+      </c>
+      <c r="M885" s="1">
+        <v>53.3333321</v>
+      </c>
+      <c r="N885" s="1"/>
+      <c r="O885" s="1"/>
+      <c r="P885" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q885" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A886" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B886" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C886" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D886" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E886" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F886" s="1">
+        <v>17</v>
+      </c>
+      <c r="G886" s="1">
+        <v>15</v>
+      </c>
+      <c r="H886" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I886" s="1">
+        <v>4.4666667000000002</v>
+      </c>
+      <c r="J886" s="1">
+        <v>0.63994050000000002</v>
+      </c>
+      <c r="K886" s="1">
+        <v>3</v>
+      </c>
+      <c r="L886" s="1">
+        <v>1</v>
+      </c>
+      <c r="M886" s="1">
+        <v>6.6666665099999998</v>
+      </c>
+      <c r="N886" s="1"/>
+      <c r="O886" s="1"/>
+      <c r="P886" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q886" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A887" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B887" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C887" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D887" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E887" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F887" s="1">
+        <v>17</v>
+      </c>
+      <c r="G887" s="1">
+        <v>15</v>
+      </c>
+      <c r="H887" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I887" s="1">
+        <v>4.4666667000000002</v>
+      </c>
+      <c r="J887" s="1">
+        <v>0.63994050000000002</v>
+      </c>
+      <c r="K887" s="1">
+        <v>4</v>
+      </c>
+      <c r="L887" s="1">
+        <v>6</v>
+      </c>
+      <c r="M887" s="1">
+        <v>40</v>
+      </c>
+      <c r="N887" s="1"/>
+      <c r="O887" s="1"/>
+      <c r="P887" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q887" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A888" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C888" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D888" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E888" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F888" s="1">
+        <v>17</v>
+      </c>
+      <c r="G888" s="1">
+        <v>15</v>
+      </c>
+      <c r="H888" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I888" s="1">
+        <v>4.4666667000000002</v>
+      </c>
+      <c r="J888" s="1">
+        <v>0.63994050000000002</v>
+      </c>
+      <c r="K888" s="1">
+        <v>5</v>
+      </c>
+      <c r="L888" s="1">
+        <v>8</v>
+      </c>
+      <c r="M888" s="1">
+        <v>53.3333321</v>
+      </c>
+      <c r="N888" s="1"/>
+      <c r="O888" s="1"/>
+      <c r="P888" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q888" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A889" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B889" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C889" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D889" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E889" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F889" s="1">
+        <v>17</v>
+      </c>
+      <c r="G889" s="1">
+        <v>15</v>
+      </c>
+      <c r="H889" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I889" s="1">
+        <v>4.7333331100000002</v>
+      </c>
+      <c r="J889" s="1">
+        <v>0.45773771000000002</v>
+      </c>
+      <c r="K889" s="1">
+        <v>4</v>
+      </c>
+      <c r="L889" s="1">
+        <v>4</v>
+      </c>
+      <c r="M889" s="1">
+        <v>26.666665999999999</v>
+      </c>
+      <c r="N889" s="1"/>
+      <c r="O889" s="1"/>
+      <c r="P889" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q889" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A890" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B890" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C890" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D890" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E890" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F890" s="1">
+        <v>17</v>
+      </c>
+      <c r="G890" s="1">
+        <v>15</v>
+      </c>
+      <c r="H890" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I890" s="1">
+        <v>4.7333331100000002</v>
+      </c>
+      <c r="J890" s="1">
+        <v>0.45773771000000002</v>
+      </c>
+      <c r="K890" s="1">
+        <v>5</v>
+      </c>
+      <c r="L890" s="1">
+        <v>11</v>
+      </c>
+      <c r="M890" s="1">
+        <v>73.333335899999994</v>
+      </c>
+      <c r="N890" s="1"/>
+      <c r="O890" s="1"/>
+      <c r="P890" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q890" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A891" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B891" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C891" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D891" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E891" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F891" s="1">
+        <v>17</v>
+      </c>
+      <c r="G891" s="1">
+        <v>15</v>
+      </c>
+      <c r="H891" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I891" s="1">
+        <v>4.6666665099999998</v>
+      </c>
+      <c r="J891" s="1">
+        <v>0.48795002999999998</v>
+      </c>
+      <c r="K891" s="1">
+        <v>4</v>
+      </c>
+      <c r="L891" s="1">
+        <v>5</v>
+      </c>
+      <c r="M891" s="1">
+        <v>33.3333321</v>
+      </c>
+      <c r="N891" s="1"/>
+      <c r="O891" s="1"/>
+      <c r="P891" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q891" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A892" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B892" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C892" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D892" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E892" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F892" s="1">
+        <v>17</v>
+      </c>
+      <c r="G892" s="1">
+        <v>15</v>
+      </c>
+      <c r="H892" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I892" s="1">
+        <v>4.6666665099999998</v>
+      </c>
+      <c r="J892" s="1">
+        <v>0.48795002999999998</v>
+      </c>
+      <c r="K892" s="1">
+        <v>5</v>
+      </c>
+      <c r="L892" s="1">
+        <v>10</v>
+      </c>
+      <c r="M892" s="1">
+        <v>66.666664100000006</v>
+      </c>
+      <c r="N892" s="1"/>
+      <c r="O892" s="1"/>
+      <c r="P892" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q892" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A893" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B893" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C893" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D893" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E893" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F893" s="1">
+        <v>17</v>
+      </c>
+      <c r="G893" s="1">
+        <v>15</v>
+      </c>
+      <c r="H893" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I893" s="1">
+        <v>4.7333331100000002</v>
+      </c>
+      <c r="J893" s="1">
+        <v>0.45773771000000002</v>
+      </c>
+      <c r="K893" s="1">
+        <v>4</v>
+      </c>
+      <c r="L893" s="1">
+        <v>4</v>
+      </c>
+      <c r="M893" s="1">
+        <v>26.666665999999999</v>
+      </c>
+      <c r="N893" s="1"/>
+      <c r="O893" s="1"/>
+      <c r="P893" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q893" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A894" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B894" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C894" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D894" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E894" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F894" s="1">
+        <v>17</v>
+      </c>
+      <c r="G894" s="1">
+        <v>15</v>
+      </c>
+      <c r="H894" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I894" s="1">
+        <v>4.7333331100000002</v>
+      </c>
+      <c r="J894" s="1">
+        <v>0.45773771000000002</v>
+      </c>
+      <c r="K894" s="1">
+        <v>5</v>
+      </c>
+      <c r="L894" s="1">
+        <v>11</v>
+      </c>
+      <c r="M894" s="1">
+        <v>73.333335899999994</v>
+      </c>
+      <c r="N894" s="1"/>
+      <c r="O894" s="1"/>
+      <c r="P894" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q894" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A895" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B895" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C895" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D895" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E895" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F895" s="1">
+        <v>17</v>
+      </c>
+      <c r="G895" s="1">
+        <v>15</v>
+      </c>
+      <c r="H895" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I895" s="1">
+        <v>4.6666665099999998</v>
+      </c>
+      <c r="J895" s="1">
+        <v>0.48795002999999998</v>
+      </c>
+      <c r="K895" s="1">
+        <v>4</v>
+      </c>
+      <c r="L895" s="1">
+        <v>5</v>
+      </c>
+      <c r="M895" s="1">
+        <v>33.3333321</v>
+      </c>
+      <c r="N895" s="1"/>
+      <c r="O895" s="1"/>
+      <c r="P895" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q895" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A896" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B896" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C896" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D896" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E896" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F896" s="1">
+        <v>17</v>
+      </c>
+      <c r="G896" s="1">
+        <v>15</v>
+      </c>
+      <c r="H896" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I896" s="1">
+        <v>4.6666665099999998</v>
+      </c>
+      <c r="J896" s="1">
+        <v>0.48795002999999998</v>
+      </c>
+      <c r="K896" s="1">
+        <v>5</v>
+      </c>
+      <c r="L896" s="1">
+        <v>10</v>
+      </c>
+      <c r="M896" s="1">
+        <v>66.666664100000006</v>
+      </c>
+      <c r="N896" s="1"/>
+      <c r="O896" s="1"/>
+      <c r="P896" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q896" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A897" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C897" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D897" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E897" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F897" s="1">
+        <v>17</v>
+      </c>
+      <c r="G897" s="1">
+        <v>15</v>
+      </c>
+      <c r="H897" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I897" s="1">
+        <v>4.5333332999999998</v>
+      </c>
+      <c r="J897" s="1">
+        <v>0.51639776999999998</v>
+      </c>
+      <c r="K897" s="1">
+        <v>4</v>
+      </c>
+      <c r="L897" s="1">
+        <v>7</v>
+      </c>
+      <c r="M897" s="1">
+        <v>46.6666679</v>
+      </c>
+      <c r="N897" s="1"/>
+      <c r="O897" s="1"/>
+      <c r="P897" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q897" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A898" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B898" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C898" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D898" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E898" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F898" s="1">
+        <v>17</v>
+      </c>
+      <c r="G898" s="1">
+        <v>15</v>
+      </c>
+      <c r="H898" s="1">
+        <v>88.235290500000005</v>
+      </c>
+      <c r="I898" s="1">
+        <v>4.5333332999999998</v>
+      </c>
+      <c r="J898" s="1">
+        <v>0.51639776999999998</v>
+      </c>
+      <c r="K898" s="1">
+        <v>5</v>
+      </c>
+      <c r="L898" s="1">
+        <v>8</v>
+      </c>
+      <c r="M898" s="1">
+        <v>53.3333321</v>
+      </c>
+      <c r="N898" s="1"/>
+      <c r="O898" s="1"/>
+      <c r="P898" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q898" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
